--- a/backend/src/data/hospital-data.xlsx
+++ b/backend/src/data/hospital-data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14631" uniqueCount="3400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14669" uniqueCount="3415">
   <si>
     <t>User ID</t>
   </si>
@@ -9826,6 +9826,21 @@
     <t>31/5/2026, 3:54:32 pm</t>
   </si>
   <si>
+    <t>176a8541</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:32:11.787Z</t>
+  </si>
+  <si>
+    <t>588dcae4</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:32:53.833Z</t>
+  </si>
+  <si>
     <t>Bill Items</t>
   </si>
   <si>
@@ -10220,6 +10235,36 @@
   </si>
   <si>
     <t>2026-06-06T08:37:49.058Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:16:04.879Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:16:06.546Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:16:24.119Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:16:25.565Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:32:12.172Z</t>
+  </si>
+  <si>
+    <t>Medicine Dispensed</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:32:12.560Z</t>
+  </si>
+  <si>
+    <t>DISPENSE_MEDICINE</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:32:54.194Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T06:32:54.541Z</t>
   </si>
 </sst>
 </file>
@@ -10699,7 +10744,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -10712,825 +10757,913 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3306</v>
+        <v>3311</v>
       </c>
       <c r="B1" t="s">
-        <v>3307</v>
+        <v>3312</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3308</v>
+        <v>3313</v>
       </c>
       <c r="E1" t="s">
-        <v>3309</v>
+        <v>3314</v>
       </c>
       <c r="F1" t="s">
-        <v>3310</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3311</v>
+        <v>3316</v>
       </c>
       <c r="C2" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E2" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3314</v>
+        <v>3319</v>
       </c>
       <c r="C3" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E3" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3315</v>
+        <v>3320</v>
       </c>
       <c r="C4" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E4" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3316</v>
+        <v>3321</v>
       </c>
       <c r="C5" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E5" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>3322</v>
+      </c>
+      <c r="C6" t="s">
         <v>3317</v>
       </c>
-      <c r="C6" t="s">
-        <v>3312</v>
-      </c>
       <c r="E6" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3319</v>
+        <v>3324</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3321</v>
+        <v>3326</v>
       </c>
       <c r="C8" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E8" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3322</v>
+        <v>3327</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>3328</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E10" t="s">
         <v>3323</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3312</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3318</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3324</v>
+        <v>3329</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3325</v>
+        <v>3330</v>
       </c>
       <c r="C12" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E12" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3326</v>
+        <v>3331</v>
       </c>
       <c r="C13" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E13" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3327</v>
+        <v>3332</v>
       </c>
       <c r="C14" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E14" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3328</v>
+        <v>3333</v>
       </c>
       <c r="C15" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E15" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3329</v>
+        <v>3334</v>
       </c>
       <c r="C16" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E16" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3330</v>
+        <v>3335</v>
       </c>
       <c r="C17" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E17" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3331</v>
+        <v>3336</v>
       </c>
       <c r="C18" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E18" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3332</v>
+        <v>3337</v>
       </c>
       <c r="C19" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E19" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3333</v>
+        <v>3338</v>
       </c>
       <c r="C20" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E20" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3334</v>
+        <v>3339</v>
       </c>
       <c r="C21" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E21" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3335</v>
+        <v>3340</v>
       </c>
       <c r="C22" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E22" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3336</v>
+        <v>3341</v>
       </c>
       <c r="C23" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E23" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3337</v>
+        <v>3342</v>
       </c>
       <c r="C24" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E24" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3338</v>
+        <v>3343</v>
       </c>
       <c r="C25" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E25" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3339</v>
+        <v>3344</v>
       </c>
       <c r="C26" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E26" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3340</v>
+        <v>3345</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3341</v>
+        <v>3346</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>3342</v>
+        <v>3347</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3343</v>
+        <v>3348</v>
       </c>
       <c r="C29" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E29" t="s">
-        <v>3344</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3345</v>
+        <v>3350</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>3346</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3347</v>
+        <v>3352</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>3348</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3349</v>
+        <v>3354</v>
       </c>
       <c r="C32" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>3348</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3350</v>
+        <v>3355</v>
       </c>
       <c r="C33" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E33" t="s">
-        <v>3351</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3352</v>
+        <v>3357</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>3353</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3354</v>
+        <v>3359</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>3355</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3356</v>
+        <v>3361</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>3355</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3357</v>
+        <v>3362</v>
       </c>
       <c r="C37" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E37" t="s">
-        <v>3358</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3359</v>
+        <v>3364</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>3360</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3361</v>
+        <v>3366</v>
       </c>
       <c r="C39" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E39" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3362</v>
+        <v>3367</v>
       </c>
       <c r="C40" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E40" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3363</v>
+        <v>3368</v>
       </c>
       <c r="C41" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E41" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3364</v>
+        <v>3369</v>
       </c>
       <c r="C42" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E42" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3365</v>
+        <v>3370</v>
       </c>
       <c r="C43" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E43" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3366</v>
+        <v>3371</v>
       </c>
       <c r="C44" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E44" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3367</v>
+        <v>3372</v>
       </c>
       <c r="C45" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E45" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3368</v>
+        <v>3373</v>
       </c>
       <c r="C46" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E46" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3369</v>
+        <v>3374</v>
       </c>
       <c r="C47" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E47" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3370</v>
+        <v>3375</v>
       </c>
       <c r="C48" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E48" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3371</v>
+        <v>3376</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3372</v>
+        <v>3377</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>3342</v>
+        <v>3347</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3373</v>
+        <v>3378</v>
       </c>
       <c r="C51" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E51" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3374</v>
+        <v>3379</v>
       </c>
       <c r="C52" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E52" t="s">
-        <v>3375</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3376</v>
+        <v>3381</v>
       </c>
       <c r="C53" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E53" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3377</v>
+        <v>3382</v>
       </c>
       <c r="C54" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E54" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3378</v>
+        <v>3383</v>
       </c>
       <c r="C55" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E55" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3379</v>
+        <v>3384</v>
       </c>
       <c r="C56" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E56" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3380</v>
+        <v>3385</v>
       </c>
       <c r="C57" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E57" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3381</v>
+        <v>3386</v>
       </c>
       <c r="C58" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E58" t="s">
-        <v>3375</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3382</v>
+        <v>3387</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3383</v>
+        <v>3388</v>
       </c>
       <c r="C60" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E60" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3384</v>
+        <v>3389</v>
       </c>
       <c r="C61" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E61" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3385</v>
+        <v>3390</v>
       </c>
       <c r="C62" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E62" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3386</v>
+        <v>3391</v>
       </c>
       <c r="C63" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E63" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3387</v>
+        <v>3392</v>
       </c>
       <c r="C64" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E64" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3388</v>
+        <v>3393</v>
       </c>
       <c r="C65" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E65" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3389</v>
+        <v>3394</v>
       </c>
       <c r="C66" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E66" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3390</v>
+        <v>3395</v>
       </c>
       <c r="C67" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E67" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3391</v>
+        <v>3396</v>
       </c>
       <c r="C68" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E68" t="s">
-        <v>3392</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3393</v>
+        <v>3398</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>3394</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3395</v>
+        <v>3400</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>3355</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3396</v>
+        <v>3401</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>3355</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3397</v>
+        <v>3402</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>3355</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3398</v>
+        <v>3403</v>
       </c>
       <c r="C73" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E73" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3399</v>
+        <v>3404</v>
       </c>
       <c r="C74" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="E74" t="s">
-        <v>3313</v>
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>3405</v>
+      </c>
+      <c r="C75" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E75" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E76" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E77" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>3408</v>
+      </c>
+      <c r="C78" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E78" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E79" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>3411</v>
+      </c>
+      <c r="C80" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>3413</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E81" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>3414</v>
+      </c>
+      <c r="C82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>3412</v>
       </c>
     </row>
   </sheetData>
@@ -66730,7 +66863,7 @@
         <v>3145</v>
       </c>
       <c r="D2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -67673,7 +67806,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
@@ -67740,6 +67873,70 @@
       </c>
       <c r="G2" t="s">
         <v>3267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D3" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>3269</v>
+      </c>
+      <c r="J3" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D4" t="s">
+        <v>627</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3144</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>3269</v>
+      </c>
+      <c r="J4" t="s">
+        <v>3272</v>
       </c>
     </row>
   </sheetData>
@@ -67771,37 +67968,37 @@
         <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>3268</v>
+        <v>3273</v>
       </c>
       <c r="E1" t="s">
-        <v>3269</v>
+        <v>3274</v>
       </c>
       <c r="F1" t="s">
-        <v>3270</v>
+        <v>3275</v>
       </c>
       <c r="G1" t="s">
-        <v>3271</v>
+        <v>3276</v>
       </c>
       <c r="H1" t="s">
-        <v>3272</v>
+        <v>3277</v>
       </c>
       <c r="I1" t="s">
         <v>3261</v>
       </c>
       <c r="J1" t="s">
-        <v>3273</v>
+        <v>3278</v>
       </c>
       <c r="K1" t="s">
-        <v>3274</v>
+        <v>3279</v>
       </c>
       <c r="L1" t="s">
-        <v>3275</v>
+        <v>3280</v>
       </c>
       <c r="M1" t="s">
         <v>33</v>
       </c>
       <c r="N1" t="s">
-        <v>3276</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
@@ -67809,10 +68006,10 @@
         <v>627</v>
       </c>
       <c r="C2" t="s">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="D2" t="s">
-        <v>3278</v>
+        <v>3283</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -67824,13 +68021,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>3279</v>
+        <v>3284</v>
       </c>
       <c r="M2" t="s">
-        <v>3280</v>
+        <v>3285</v>
       </c>
       <c r="N2" t="s">
-        <v>3281</v>
+        <v>3286</v>
       </c>
     </row>
   </sheetData>
@@ -67854,7 +68051,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3282</v>
+        <v>3287</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -67866,82 +68063,82 @@
         <v>617</v>
       </c>
       <c r="E1" t="s">
-        <v>3283</v>
+        <v>3288</v>
       </c>
       <c r="F1" t="s">
-        <v>3284</v>
+        <v>3289</v>
       </c>
       <c r="G1" t="s">
         <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>3285</v>
+        <v>3290</v>
       </c>
       <c r="I1" t="s">
-        <v>3286</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3287</v>
+        <v>3292</v>
       </c>
       <c r="B2" t="s">
-        <v>3288</v>
+        <v>3293</v>
       </c>
       <c r="C2" t="s">
-        <v>3289</v>
+        <v>3294</v>
       </c>
       <c r="D2" t="s">
-        <v>3290</v>
+        <v>3295</v>
       </c>
       <c r="E2" t="s">
-        <v>3291</v>
+        <v>3296</v>
       </c>
       <c r="F2" t="s">
         <v>612</v>
       </c>
       <c r="G2" t="s">
-        <v>3292</v>
+        <v>3297</v>
       </c>
       <c r="H2" t="s">
-        <v>3293</v>
+        <v>3298</v>
       </c>
       <c r="I2" t="s">
-        <v>3294</v>
+        <v>3299</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3295</v>
+        <v>3300</v>
       </c>
       <c r="B3" t="s">
-        <v>3296</v>
+        <v>3301</v>
       </c>
       <c r="C3" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="G3" t="s">
         <v>3297</v>
       </c>
-      <c r="D3" t="s">
-        <v>3298</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3299</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3300</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3292</v>
-      </c>
       <c r="H3" t="s">
-        <v>3301</v>
+        <v>3306</v>
       </c>
       <c r="I3" t="s">
-        <v>3302</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3303</v>
+        <v>3308</v>
       </c>
       <c r="B4" t="s">
         <v>627</v>
@@ -67953,10 +68150,10 @@
         <v>612</v>
       </c>
       <c r="G4" t="s">
-        <v>3304</v>
+        <v>3309</v>
       </c>
       <c r="H4" t="s">
-        <v>3305</v>
+        <v>3310</v>
       </c>
       <c r="I4" t="s">
         <v>627</v>

--- a/backend/src/data/hospital-data.xlsx
+++ b/backend/src/data/hospital-data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14669" uniqueCount="3415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15125" uniqueCount="3570">
   <si>
     <t>User ID</t>
   </si>
@@ -9439,6 +9439,15 @@
     <t>2026-06-06T07:15:43.584Z</t>
   </si>
   <si>
+    <t>d07575a8</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:10:41.987Z</t>
+  </si>
+  <si>
     <t>Medicine ID</t>
   </si>
   <si>
@@ -9841,6 +9850,12 @@
     <t>2026-06-08T06:32:53.833Z</t>
   </si>
   <si>
+    <t>1b17c292</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:53:39.256Z</t>
+  </si>
+  <si>
     <t>Bill Items</t>
   </si>
   <si>
@@ -9883,6 +9898,42 @@
     <t>2026-06-06T08:27:09.920Z</t>
   </si>
   <si>
+    <t>[{"serviceName":"Registration Fee","category":"Registration","amount":200}]</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:54:49.468Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:09:44.506Z</t>
+  </si>
+  <si>
+    <t>BILL-C2D219</t>
+  </si>
+  <si>
+    <t>UPI</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:15:56.924Z</t>
+  </si>
+  <si>
+    <t>BILL-45C852</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:18:34.046Z</t>
+  </si>
+  <si>
+    <t>BILL-93157A</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:50.766Z</t>
+  </si>
+  <si>
     <t>Procedure ID</t>
   </si>
   <si>
@@ -9913,9 +9964,6 @@
     <t>Joint Aspiration</t>
   </si>
   <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
     <t>10:00</t>
   </si>
   <si>
@@ -9949,9 +9997,6 @@
     <t>OT-6E31AB</t>
   </si>
   <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
     <t>2026-06-06T00:00:00.000Z</t>
   </si>
   <si>
@@ -10265,6 +10310,426 @@
   </si>
   <si>
     <t>2026-06-08T06:32:54.541Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:58:33.115Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:58:35.146Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:35:50.233Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:35:52.051Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:36:37.556Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:36:39.104Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:37:08.658Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:37:21.001Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:37:22.315Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:37:30.742Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:37:32.072Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:39:31.185Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:39:31.497Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:39:51.241Z</t>
+  </si>
+  <si>
+    <t>DELETE_TEST</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:42:07.064Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:42:08.960Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:53:39.679Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:53:40.058Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:54:49.770Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:54:50.057Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:09:27.558Z</t>
+  </si>
+  <si>
+    <t>UPDATE_BILL</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:09:30.345Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:09:44.848Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:09:45.154Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:15:57.336Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:15:57.750Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:18:34.395Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:18:34.773Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:28.818Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:29.137Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:33.804Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:40.222Z</t>
+  </si>
+  <si>
+    <t>DELETE_BILL</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:51.089Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:19:51.410Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:22:01.395Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:22:02.611Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:22:23.387Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:22:24.769Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:22:26.852Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:22:28.139Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:33:36.611Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:33:37.744Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:34:04.697Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:34:48.463Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:34:54.117Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:34:58.028Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:35:04.096Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T09:35:28.462Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:02.376Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:10.606Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:12.231Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:19.449Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:21.177Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:49.341Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:50.881Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:15.067Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:16.801Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:24.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:25.753Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:34.448Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:35.855Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:38.374Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:40.235Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:10:42.273Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:10:42.603Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:10:48.986Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:10:56.380Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:11:06.362Z</t>
+  </si>
+  <si>
+    <t>UPDATE_OT</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:11:09.581Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:11:13.168Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:11:36.005Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:12:16.915Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:12:17.988Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:12:21.611Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:12:25.132Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:12:29.052Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:13:44.393Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:13:46.059Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:14:30.539Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:14:31.903Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:14:40.243Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:14:41.456Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:14:45.298Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:14:46.352Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:17:47.028Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:17:48.402Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:20:02.944Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:20:03.890Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:20:15.654Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:20:16.928Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:20:22.710Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:20:23.929Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:23:40.409Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:23:41.892Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:24:52.127Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:24:53.077Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:26:42.394Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:26:43.780Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:26:48.771Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:26:50.024Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:28:44.414Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:28:46.060Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:29:11.411Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:29:12.243Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:31:11.929Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:31:12.881Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:31:29.790Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:31:31.743Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:31:54.647Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:31:56.063Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:32:07.283Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:32:08.628Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:36:45.602Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:36:47.173Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:06.929Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:08.418Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:15.107Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:16.912Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:21.751Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:23.212Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:55.847Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:39:57.506Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:41:54.882Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:41:56.021Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:42:07.313Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:42:08.603Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:42:19.403Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:42:20.321Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:43:19.376Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:43:20.221Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:43:26.749Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:43:27.899Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:44:04.718Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:44:05.905Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:46:11.217Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:46:12.080Z</t>
   </si>
 </sst>
 </file>
@@ -10744,7 +11209,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F218"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -10757,913 +11222,2409 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3311</v>
+        <v>3326</v>
       </c>
       <c r="B1" t="s">
-        <v>3312</v>
+        <v>3327</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3313</v>
+        <v>3328</v>
       </c>
       <c r="E1" t="s">
-        <v>3314</v>
+        <v>3329</v>
       </c>
       <c r="F1" t="s">
-        <v>3315</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3316</v>
+        <v>3331</v>
       </c>
       <c r="C2" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E2" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3319</v>
+        <v>3334</v>
       </c>
       <c r="C3" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E3" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3320</v>
+        <v>3335</v>
       </c>
       <c r="C4" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E4" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3321</v>
+        <v>3336</v>
       </c>
       <c r="C5" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E5" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3322</v>
+        <v>3337</v>
       </c>
       <c r="C6" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E6" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3324</v>
+        <v>3339</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>3325</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3326</v>
+        <v>3341</v>
       </c>
       <c r="C8" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E8" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3327</v>
+        <v>3342</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>3325</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3328</v>
+        <v>3343</v>
       </c>
       <c r="C10" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E10" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3329</v>
+        <v>3344</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>3325</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3330</v>
+        <v>3345</v>
       </c>
       <c r="C12" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E12" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3331</v>
+        <v>3346</v>
       </c>
       <c r="C13" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E13" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>3347</v>
+      </c>
+      <c r="C14" t="s">
         <v>3332</v>
       </c>
-      <c r="C14" t="s">
-        <v>3317</v>
-      </c>
       <c r="E14" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>3348</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E15" t="s">
         <v>3333</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3317</v>
-      </c>
-      <c r="E15" t="s">
-        <v>3318</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3334</v>
+        <v>3349</v>
       </c>
       <c r="C16" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E16" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3335</v>
+        <v>3350</v>
       </c>
       <c r="C17" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E17" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3336</v>
+        <v>3351</v>
       </c>
       <c r="C18" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E18" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3337</v>
+        <v>3352</v>
       </c>
       <c r="C19" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E19" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3338</v>
+        <v>3353</v>
       </c>
       <c r="C20" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E20" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3339</v>
+        <v>3354</v>
       </c>
       <c r="C21" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E21" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3340</v>
+        <v>3355</v>
       </c>
       <c r="C22" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E22" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3341</v>
+        <v>3356</v>
       </c>
       <c r="C23" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E23" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3342</v>
+        <v>3357</v>
       </c>
       <c r="C24" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E24" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3343</v>
+        <v>3358</v>
       </c>
       <c r="C25" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E25" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3344</v>
+        <v>3359</v>
       </c>
       <c r="C26" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E26" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3345</v>
+        <v>3360</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>3325</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3346</v>
+        <v>3361</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>3347</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3348</v>
+        <v>3363</v>
       </c>
       <c r="C29" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E29" t="s">
-        <v>3349</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3350</v>
+        <v>3365</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>3351</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3352</v>
+        <v>3367</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>3353</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3354</v>
+        <v>3369</v>
       </c>
       <c r="C32" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>3353</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3355</v>
+        <v>3370</v>
       </c>
       <c r="C33" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E33" t="s">
-        <v>3356</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3357</v>
+        <v>3372</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>3358</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3359</v>
+        <v>3374</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>3360</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3361</v>
+        <v>3376</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>3360</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3362</v>
+        <v>3377</v>
       </c>
       <c r="C37" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E37" t="s">
-        <v>3363</v>
+        <v>3378</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3364</v>
+        <v>3379</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>3365</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3366</v>
+        <v>3381</v>
       </c>
       <c r="C39" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E39" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3367</v>
+        <v>3382</v>
       </c>
       <c r="C40" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E40" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3368</v>
+        <v>3383</v>
       </c>
       <c r="C41" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E41" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3369</v>
+        <v>3384</v>
       </c>
       <c r="C42" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E42" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3370</v>
+        <v>3385</v>
       </c>
       <c r="C43" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E43" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3371</v>
+        <v>3386</v>
       </c>
       <c r="C44" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E44" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3372</v>
+        <v>3387</v>
       </c>
       <c r="C45" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E45" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3373</v>
+        <v>3388</v>
       </c>
       <c r="C46" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E46" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3374</v>
+        <v>3389</v>
       </c>
       <c r="C47" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E47" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3375</v>
+        <v>3390</v>
       </c>
       <c r="C48" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E48" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3376</v>
+        <v>3391</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>3325</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3377</v>
+        <v>3392</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>3347</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3378</v>
+        <v>3393</v>
       </c>
       <c r="C51" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E51" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3379</v>
+        <v>3394</v>
       </c>
       <c r="C52" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E52" t="s">
-        <v>3380</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3381</v>
+        <v>3396</v>
       </c>
       <c r="C53" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E53" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3382</v>
+        <v>3397</v>
       </c>
       <c r="C54" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E54" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3383</v>
+        <v>3398</v>
       </c>
       <c r="C55" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E55" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3384</v>
+        <v>3399</v>
       </c>
       <c r="C56" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E56" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3385</v>
+        <v>3400</v>
       </c>
       <c r="C57" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E57" t="s">
-        <v>3323</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3386</v>
+        <v>3401</v>
       </c>
       <c r="C58" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E58" t="s">
-        <v>3380</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3387</v>
+        <v>3402</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>3325</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3388</v>
+        <v>3403</v>
       </c>
       <c r="C60" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E60" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3389</v>
+        <v>3404</v>
       </c>
       <c r="C61" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E61" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3390</v>
+        <v>3405</v>
       </c>
       <c r="C62" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E62" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3391</v>
+        <v>3406</v>
       </c>
       <c r="C63" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E63" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3392</v>
+        <v>3407</v>
       </c>
       <c r="C64" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E64" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3393</v>
+        <v>3408</v>
       </c>
       <c r="C65" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E65" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3394</v>
+        <v>3409</v>
       </c>
       <c r="C66" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E66" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3395</v>
+        <v>3410</v>
       </c>
       <c r="C67" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E67" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3396</v>
+        <v>3411</v>
       </c>
       <c r="C68" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E68" t="s">
-        <v>3397</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3398</v>
+        <v>3413</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>3399</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3400</v>
+        <v>3415</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>3360</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3401</v>
+        <v>3416</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>3360</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3402</v>
+        <v>3417</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>3360</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3403</v>
+        <v>3418</v>
       </c>
       <c r="C73" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E73" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3404</v>
+        <v>3419</v>
       </c>
       <c r="C74" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E74" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3405</v>
+        <v>3420</v>
       </c>
       <c r="C75" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E75" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3406</v>
+        <v>3421</v>
       </c>
       <c r="C76" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E76" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3407</v>
+        <v>3422</v>
       </c>
       <c r="C77" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E77" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3408</v>
+        <v>3423</v>
       </c>
       <c r="C78" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E78" t="s">
-        <v>3318</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3409</v>
+        <v>3424</v>
       </c>
       <c r="C79" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E79" t="s">
-        <v>3410</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3411</v>
+        <v>3426</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
       </c>
       <c r="E80" t="s">
-        <v>3412</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3413</v>
+        <v>3428</v>
       </c>
       <c r="C81" t="s">
-        <v>3317</v>
+        <v>3332</v>
       </c>
       <c r="E81" t="s">
-        <v>3410</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3414</v>
+        <v>3429</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
       </c>
       <c r="E82" t="s">
+        <v>3427</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>3430</v>
+      </c>
+      <c r="C83" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>3431</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E84" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C85" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E85" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>3433</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>3434</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E87" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>3435</v>
+      </c>
+      <c r="C88" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E88" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>3436</v>
+      </c>
+      <c r="C89" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E89" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>3437</v>
+      </c>
+      <c r="C90" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E90" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>3438</v>
+      </c>
+      <c r="C91" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E91" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>3439</v>
+      </c>
+      <c r="C92" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E92" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C93" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E93" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>3441</v>
+      </c>
+      <c r="C94" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E94" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>3442</v>
+      </c>
+      <c r="C95" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C96" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" t="s">
+        <v>3444</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>3445</v>
+      </c>
+      <c r="C97" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E97" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C98" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E98" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>3447</v>
+      </c>
+      <c r="C99" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E99" t="s">
+        <v>3425</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" t="s">
+        <v>3427</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>3449</v>
+      </c>
+      <c r="C101" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E101" t="s">
         <v>3412</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>3450</v>
+      </c>
+      <c r="C102" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>3451</v>
+      </c>
+      <c r="C103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>3454</v>
+      </c>
+      <c r="C105" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E105" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>3455</v>
+      </c>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>3456</v>
+      </c>
+      <c r="C107" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E107" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>3457</v>
+      </c>
+      <c r="C108" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>3458</v>
+      </c>
+      <c r="C109" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E109" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>3459</v>
+      </c>
+      <c r="C110" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>3460</v>
+      </c>
+      <c r="C111" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E111" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>3461</v>
+      </c>
+      <c r="C112" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>3462</v>
+      </c>
+      <c r="C113" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>3463</v>
+      </c>
+      <c r="C114" t="s">
+        <v>8</v>
+      </c>
+      <c r="E114" t="s">
+        <v>3464</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>3465</v>
+      </c>
+      <c r="C115" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E115" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>3466</v>
+      </c>
+      <c r="C116" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>3467</v>
+      </c>
+      <c r="C117" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E117" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>3468</v>
+      </c>
+      <c r="C118" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E118" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C119" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E119" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>3470</v>
+      </c>
+      <c r="C120" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E120" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>3471</v>
+      </c>
+      <c r="C121" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E121" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>3472</v>
+      </c>
+      <c r="C122" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E122" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>3473</v>
+      </c>
+      <c r="C123" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E123" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>3474</v>
+      </c>
+      <c r="C124" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E124" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C125" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E125" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>3476</v>
+      </c>
+      <c r="C126" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E126" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>3477</v>
+      </c>
+      <c r="C127" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E127" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C128" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E128" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C129" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E129" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>3480</v>
+      </c>
+      <c r="C130" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E130" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C131" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E131" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>3482</v>
+      </c>
+      <c r="C132" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E132" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>3483</v>
+      </c>
+      <c r="C133" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E133" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C134" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E134" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C135" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E135" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C136" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E136" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>3487</v>
+      </c>
+      <c r="C137" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E137" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>3488</v>
+      </c>
+      <c r="C138" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E138" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>3489</v>
+      </c>
+      <c r="C139" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E139" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>3490</v>
+      </c>
+      <c r="C140" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E140" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>3491</v>
+      </c>
+      <c r="C141" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E141" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>3492</v>
+      </c>
+      <c r="C142" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E142" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C143" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E143" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C144" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E144" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>3495</v>
+      </c>
+      <c r="C145" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E145" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>3496</v>
+      </c>
+      <c r="C146" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E146" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C147" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>3498</v>
+      </c>
+      <c r="C148" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" t="s">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>3499</v>
+      </c>
+      <c r="C149" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" t="s">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>3500</v>
+      </c>
+      <c r="C150" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C151" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C152" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>3504</v>
+      </c>
+      <c r="C153" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C154" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E154" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>3506</v>
+      </c>
+      <c r="C155" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E155" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C156" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E156" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C157" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E157" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C158" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E158" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>3510</v>
+      </c>
+      <c r="C159" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E159" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>3511</v>
+      </c>
+      <c r="C160" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E160" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>3512</v>
+      </c>
+      <c r="C161" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E161" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>3513</v>
+      </c>
+      <c r="C162" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E162" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>3514</v>
+      </c>
+      <c r="C163" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E163" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>3515</v>
+      </c>
+      <c r="C164" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E164" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>3516</v>
+      </c>
+      <c r="C165" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E165" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>3517</v>
+      </c>
+      <c r="C166" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E166" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>3518</v>
+      </c>
+      <c r="C167" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E167" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>3519</v>
+      </c>
+      <c r="C168" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E168" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>3520</v>
+      </c>
+      <c r="C169" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E169" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>3521</v>
+      </c>
+      <c r="C170" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E170" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>3522</v>
+      </c>
+      <c r="C171" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E171" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>3523</v>
+      </c>
+      <c r="C172" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E172" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>3524</v>
+      </c>
+      <c r="C173" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E173" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>3525</v>
+      </c>
+      <c r="C174" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E174" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>3526</v>
+      </c>
+      <c r="C175" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E175" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>3527</v>
+      </c>
+      <c r="C176" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E176" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>3528</v>
+      </c>
+      <c r="C177" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E177" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>3529</v>
+      </c>
+      <c r="C178" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E178" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>3530</v>
+      </c>
+      <c r="C179" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E179" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>3531</v>
+      </c>
+      <c r="C180" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E180" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C181" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E181" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C182" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E182" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>3534</v>
+      </c>
+      <c r="C183" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E183" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>3535</v>
+      </c>
+      <c r="C184" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E184" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>3536</v>
+      </c>
+      <c r="C185" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E185" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>3537</v>
+      </c>
+      <c r="C186" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E186" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>3538</v>
+      </c>
+      <c r="C187" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E187" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>3539</v>
+      </c>
+      <c r="C188" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E188" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>3540</v>
+      </c>
+      <c r="C189" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E189" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>3541</v>
+      </c>
+      <c r="C190" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E190" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>3542</v>
+      </c>
+      <c r="C191" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E191" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>3543</v>
+      </c>
+      <c r="C192" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E192" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C193" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E193" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>3545</v>
+      </c>
+      <c r="C194" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E194" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C195" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E195" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>3547</v>
+      </c>
+      <c r="C196" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E196" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>3548</v>
+      </c>
+      <c r="C197" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E197" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>3549</v>
+      </c>
+      <c r="C198" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E198" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>3550</v>
+      </c>
+      <c r="C199" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E199" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>3551</v>
+      </c>
+      <c r="C200" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E200" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>3552</v>
+      </c>
+      <c r="C201" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E201" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>3553</v>
+      </c>
+      <c r="C202" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E202" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>3554</v>
+      </c>
+      <c r="C203" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E203" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>3555</v>
+      </c>
+      <c r="C204" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E204" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>3556</v>
+      </c>
+      <c r="C205" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E205" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>3557</v>
+      </c>
+      <c r="C206" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E206" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>3558</v>
+      </c>
+      <c r="C207" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E207" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>3559</v>
+      </c>
+      <c r="C208" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E208" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>3560</v>
+      </c>
+      <c r="C209" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E209" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>3561</v>
+      </c>
+      <c r="C210" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E210" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>3562</v>
+      </c>
+      <c r="C211" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E211" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>3563</v>
+      </c>
+      <c r="C212" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E212" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>3564</v>
+      </c>
+      <c r="C213" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E213" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>3565</v>
+      </c>
+      <c r="C214" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E214" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>3566</v>
+      </c>
+      <c r="C215" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E215" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>3567</v>
+      </c>
+      <c r="C216" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E216" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C217" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E217" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C218" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E218" t="s">
+        <v>3333</v>
       </c>
     </row>
   </sheetData>
@@ -66737,7 +68698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -66805,6 +68766,35 @@
       </c>
       <c r="I2" t="s">
         <v>3138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D3" t="s">
+        <v>733</v>
+      </c>
+      <c r="E3">
+        <v>500</v>
+      </c>
+      <c r="F3" t="s">
+        <v>612</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3140</v>
+      </c>
+      <c r="I3" t="s">
+        <v>3141</v>
       </c>
     </row>
   </sheetData>
@@ -66828,22 +68818,22 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3139</v>
+        <v>3142</v>
       </c>
       <c r="B1" t="s">
-        <v>3140</v>
+        <v>3143</v>
       </c>
       <c r="C1" t="s">
         <v>729</v>
       </c>
       <c r="D1" t="s">
-        <v>3141</v>
+        <v>3144</v>
       </c>
       <c r="E1" t="s">
         <v>731</v>
       </c>
       <c r="F1" t="s">
-        <v>3142</v>
+        <v>3145</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -66854,13 +68844,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3143</v>
+        <v>3146</v>
       </c>
       <c r="B2" t="s">
-        <v>3144</v>
+        <v>3147</v>
       </c>
       <c r="C2" t="s">
-        <v>3145</v>
+        <v>3148</v>
       </c>
       <c r="D2">
         <v>608</v>
@@ -66869,21 +68859,21 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
       <c r="G2" t="s">
-        <v>3147</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="B3" t="s">
-        <v>3149</v>
+        <v>3152</v>
       </c>
       <c r="C3" t="s">
-        <v>3150</v>
+        <v>3153</v>
       </c>
       <c r="D3">
         <v>309</v>
@@ -66892,21 +68882,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>3151</v>
+        <v>3154</v>
       </c>
       <c r="G3" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3153</v>
+        <v>3156</v>
       </c>
       <c r="B4" t="s">
-        <v>3154</v>
+        <v>3157</v>
       </c>
       <c r="C4" t="s">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D4">
         <v>560</v>
@@ -66915,44 +68905,44 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>3156</v>
+        <v>3159</v>
       </c>
       <c r="G4" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3157</v>
+        <v>3160</v>
       </c>
       <c r="B5" t="s">
-        <v>3158</v>
+        <v>3161</v>
       </c>
       <c r="C5" t="s">
-        <v>3159</v>
+        <v>3162</v>
       </c>
       <c r="D5">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E5">
         <v>85</v>
       </c>
       <c r="F5" t="s">
-        <v>3156</v>
+        <v>3159</v>
       </c>
       <c r="G5" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3160</v>
+        <v>3163</v>
       </c>
       <c r="B6" t="s">
-        <v>3161</v>
+        <v>3164</v>
       </c>
       <c r="C6" t="s">
-        <v>3145</v>
+        <v>3148</v>
       </c>
       <c r="D6">
         <v>200</v>
@@ -66961,21 +68951,21 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>3162</v>
+        <v>3165</v>
       </c>
       <c r="G6" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3163</v>
+        <v>3166</v>
       </c>
       <c r="B7" t="s">
-        <v>3164</v>
+        <v>3167</v>
       </c>
       <c r="C7" t="s">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D7">
         <v>250</v>
@@ -66984,21 +68974,21 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>3165</v>
+        <v>3168</v>
       </c>
       <c r="G7" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3166</v>
+        <v>3169</v>
       </c>
       <c r="B8" t="s">
-        <v>3167</v>
+        <v>3170</v>
       </c>
       <c r="C8" t="s">
-        <v>3150</v>
+        <v>3153</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -67007,21 +68997,21 @@
         <v>150</v>
       </c>
       <c r="F8" t="s">
-        <v>3165</v>
+        <v>3168</v>
       </c>
       <c r="G8" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3168</v>
+        <v>3171</v>
       </c>
       <c r="B9" t="s">
-        <v>3169</v>
+        <v>3172</v>
       </c>
       <c r="C9" t="s">
-        <v>3170</v>
+        <v>3173</v>
       </c>
       <c r="D9">
         <v>180</v>
@@ -67030,21 +69020,21 @@
         <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>3171</v>
+        <v>3174</v>
       </c>
       <c r="G9" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3172</v>
+        <v>3175</v>
       </c>
       <c r="B10" t="s">
-        <v>3173</v>
+        <v>3176</v>
       </c>
       <c r="C10" t="s">
-        <v>3174</v>
+        <v>3177</v>
       </c>
       <c r="D10">
         <v>300</v>
@@ -67053,21 +69043,21 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>3175</v>
+        <v>3178</v>
       </c>
       <c r="G10" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3176</v>
+        <v>3179</v>
       </c>
       <c r="B11" t="s">
-        <v>3177</v>
+        <v>3180</v>
       </c>
       <c r="C11" t="s">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D11">
         <v>450</v>
@@ -67076,21 +69066,21 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
       <c r="G11" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3178</v>
+        <v>3181</v>
       </c>
       <c r="B12" t="s">
-        <v>3179</v>
+        <v>3182</v>
       </c>
       <c r="C12" t="s">
-        <v>3180</v>
+        <v>3183</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -67099,21 +69089,21 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>3171</v>
+        <v>3174</v>
       </c>
       <c r="G12" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3181</v>
+        <v>3184</v>
       </c>
       <c r="B13" t="s">
-        <v>3182</v>
+        <v>3185</v>
       </c>
       <c r="C13" t="s">
-        <v>3183</v>
+        <v>3186</v>
       </c>
       <c r="D13">
         <v>350</v>
@@ -67122,21 +69112,21 @@
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="G13" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3185</v>
+        <v>3188</v>
       </c>
       <c r="B14" t="s">
+        <v>3189</v>
+      </c>
+      <c r="C14" t="s">
         <v>3186</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3183</v>
       </c>
       <c r="D14">
         <v>200</v>
@@ -67145,21 +69135,21 @@
         <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>3151</v>
+        <v>3154</v>
       </c>
       <c r="G14" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3187</v>
+        <v>3190</v>
       </c>
       <c r="B15" t="s">
-        <v>3188</v>
+        <v>3191</v>
       </c>
       <c r="C15" t="s">
-        <v>3183</v>
+        <v>3186</v>
       </c>
       <c r="D15">
         <v>250</v>
@@ -67168,21 +69158,21 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>3189</v>
+        <v>3192</v>
       </c>
       <c r="G15" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3190</v>
+        <v>3193</v>
       </c>
       <c r="B16" t="s">
-        <v>3191</v>
+        <v>3194</v>
       </c>
       <c r="C16" t="s">
-        <v>3192</v>
+        <v>3195</v>
       </c>
       <c r="D16">
         <v>300</v>
@@ -67191,21 +69181,21 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>3175</v>
+        <v>3178</v>
       </c>
       <c r="G16" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3193</v>
+        <v>3196</v>
       </c>
       <c r="B17" t="s">
-        <v>3194</v>
+        <v>3197</v>
       </c>
       <c r="C17" t="s">
-        <v>3195</v>
+        <v>3198</v>
       </c>
       <c r="D17">
         <v>250</v>
@@ -67214,21 +69204,21 @@
         <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>3156</v>
+        <v>3159</v>
       </c>
       <c r="G17" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3196</v>
+        <v>3199</v>
       </c>
       <c r="B18" t="s">
-        <v>3197</v>
+        <v>3200</v>
       </c>
       <c r="C18" t="s">
-        <v>3195</v>
+        <v>3198</v>
       </c>
       <c r="D18">
         <v>200</v>
@@ -67237,21 +69227,21 @@
         <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>3165</v>
+        <v>3168</v>
       </c>
       <c r="G18" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3198</v>
+        <v>3201</v>
       </c>
       <c r="B19" t="s">
-        <v>3199</v>
+        <v>3202</v>
       </c>
       <c r="C19" t="s">
-        <v>3200</v>
+        <v>3203</v>
       </c>
       <c r="D19">
         <v>150</v>
@@ -67260,21 +69250,21 @@
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>3171</v>
+        <v>3174</v>
       </c>
       <c r="G19" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3201</v>
+        <v>3204</v>
       </c>
       <c r="B20" t="s">
-        <v>3202</v>
+        <v>3205</v>
       </c>
       <c r="C20" t="s">
-        <v>3180</v>
+        <v>3183</v>
       </c>
       <c r="D20">
         <v>400</v>
@@ -67283,21 +69273,21 @@
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
       <c r="G20" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3203</v>
+        <v>3206</v>
       </c>
       <c r="B21" t="s">
-        <v>3204</v>
+        <v>3207</v>
       </c>
       <c r="C21" t="s">
-        <v>3205</v>
+        <v>3208</v>
       </c>
       <c r="D21">
         <v>50</v>
@@ -67306,21 +69296,21 @@
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
       <c r="G21" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3206</v>
+        <v>3209</v>
       </c>
       <c r="B22" t="s">
-        <v>3207</v>
+        <v>3210</v>
       </c>
       <c r="C22" t="s">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -67329,21 +69319,21 @@
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>3165</v>
+        <v>3168</v>
       </c>
       <c r="G22" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3208</v>
+        <v>3211</v>
       </c>
       <c r="B23" t="s">
-        <v>3209</v>
+        <v>3212</v>
       </c>
       <c r="C23" t="s">
-        <v>3210</v>
+        <v>3213</v>
       </c>
       <c r="D23">
         <v>80</v>
@@ -67352,21 +69342,21 @@
         <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="G23" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3211</v>
+        <v>3214</v>
       </c>
       <c r="B24" t="s">
-        <v>3212</v>
+        <v>3215</v>
       </c>
       <c r="C24" t="s">
-        <v>3210</v>
+        <v>3213</v>
       </c>
       <c r="D24">
         <v>50</v>
@@ -67375,21 +69365,21 @@
         <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>3213</v>
+        <v>3216</v>
       </c>
       <c r="G24" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3214</v>
+        <v>3217</v>
       </c>
       <c r="B25" t="s">
-        <v>3215</v>
+        <v>3218</v>
       </c>
       <c r="C25" t="s">
-        <v>3205</v>
+        <v>3208</v>
       </c>
       <c r="D25">
         <v>60</v>
@@ -67398,21 +69388,21 @@
         <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>3171</v>
+        <v>3174</v>
       </c>
       <c r="G25" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3216</v>
+        <v>3219</v>
       </c>
       <c r="B26" t="s">
-        <v>3217</v>
+        <v>3220</v>
       </c>
       <c r="C26" t="s">
-        <v>3150</v>
+        <v>3153</v>
       </c>
       <c r="D26">
         <v>20</v>
@@ -67421,21 +69411,21 @@
         <v>2500</v>
       </c>
       <c r="F26" t="s">
-        <v>3218</v>
+        <v>3221</v>
       </c>
       <c r="G26" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3219</v>
+        <v>3222</v>
       </c>
       <c r="B27" t="s">
-        <v>3220</v>
+        <v>3223</v>
       </c>
       <c r="C27" t="s">
-        <v>3195</v>
+        <v>3198</v>
       </c>
       <c r="D27">
         <v>200</v>
@@ -67444,21 +69434,21 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
       <c r="G27" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3221</v>
+        <v>3224</v>
       </c>
       <c r="B28" t="s">
-        <v>3222</v>
+        <v>3225</v>
       </c>
       <c r="C28" t="s">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D28">
         <v>150</v>
@@ -67467,21 +69457,21 @@
         <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>3151</v>
+        <v>3154</v>
       </c>
       <c r="G28" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3223</v>
+        <v>3226</v>
       </c>
       <c r="B29" t="s">
-        <v>3224</v>
+        <v>3227</v>
       </c>
       <c r="C29" t="s">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="D29">
         <v>180</v>
@@ -67490,21 +69480,21 @@
         <v>20</v>
       </c>
       <c r="F29" t="s">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="G29" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3225</v>
+        <v>3228</v>
       </c>
       <c r="B30" t="s">
-        <v>3226</v>
+        <v>3229</v>
       </c>
       <c r="C30" t="s">
-        <v>3159</v>
+        <v>3162</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -67513,21 +69503,21 @@
         <v>70</v>
       </c>
       <c r="F30" t="s">
-        <v>3162</v>
+        <v>3165</v>
       </c>
       <c r="G30" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3227</v>
+        <v>3230</v>
       </c>
       <c r="B31" t="s">
-        <v>3228</v>
+        <v>3231</v>
       </c>
       <c r="C31" t="s">
-        <v>3183</v>
+        <v>3186</v>
       </c>
       <c r="D31">
         <v>250</v>
@@ -67536,21 +69526,21 @@
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>3151</v>
+        <v>3154</v>
       </c>
       <c r="G31" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3229</v>
+        <v>3232</v>
       </c>
       <c r="B32" t="s">
-        <v>3230</v>
+        <v>3233</v>
       </c>
       <c r="C32" t="s">
-        <v>3183</v>
+        <v>3186</v>
       </c>
       <c r="D32">
         <v>80</v>
@@ -67559,21 +69549,21 @@
         <v>120</v>
       </c>
       <c r="F32" t="s">
-        <v>3146</v>
+        <v>3149</v>
       </c>
       <c r="G32" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3231</v>
+        <v>3234</v>
       </c>
       <c r="B33" t="s">
-        <v>3232</v>
+        <v>3235</v>
       </c>
       <c r="C33" t="s">
-        <v>3170</v>
+        <v>3173</v>
       </c>
       <c r="D33">
         <v>150</v>
@@ -67582,21 +69572,21 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>3233</v>
+        <v>3236</v>
       </c>
       <c r="G33" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3234</v>
+        <v>3237</v>
       </c>
       <c r="B34" t="s">
-        <v>3235</v>
+        <v>3238</v>
       </c>
       <c r="C34" t="s">
-        <v>3236</v>
+        <v>3239</v>
       </c>
       <c r="D34">
         <v>120</v>
@@ -67605,21 +69595,21 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>3233</v>
+        <v>3236</v>
       </c>
       <c r="G34" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3237</v>
+        <v>3240</v>
       </c>
       <c r="B35" t="s">
-        <v>3238</v>
+        <v>3241</v>
       </c>
       <c r="C35" t="s">
-        <v>3150</v>
+        <v>3153</v>
       </c>
       <c r="D35">
         <v>600</v>
@@ -67628,21 +69618,21 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>3233</v>
+        <v>3236</v>
       </c>
       <c r="G35" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3239</v>
+        <v>3242</v>
       </c>
       <c r="B36" t="s">
-        <v>3240</v>
+        <v>3243</v>
       </c>
       <c r="C36" t="s">
-        <v>3241</v>
+        <v>3244</v>
       </c>
       <c r="D36">
         <v>400</v>
@@ -67651,21 +69641,21 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>3162</v>
+        <v>3165</v>
       </c>
       <c r="G36" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3242</v>
+        <v>3245</v>
       </c>
       <c r="B37" t="s">
-        <v>3243</v>
+        <v>3246</v>
       </c>
       <c r="C37" t="s">
-        <v>3210</v>
+        <v>3213</v>
       </c>
       <c r="D37">
         <v>300</v>
@@ -67674,21 +69664,21 @@
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>3162</v>
+        <v>3165</v>
       </c>
       <c r="G37" t="s">
-        <v>3152</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3244</v>
+        <v>3247</v>
       </c>
       <c r="B38" t="s">
-        <v>3245</v>
+        <v>3248</v>
       </c>
       <c r="C38" t="s">
-        <v>3210</v>
+        <v>3213</v>
       </c>
       <c r="D38">
         <v>150</v>
@@ -67697,21 +69687,21 @@
         <v>45</v>
       </c>
       <c r="F38" t="s">
-        <v>3218</v>
+        <v>3221</v>
       </c>
       <c r="G38" t="s">
-        <v>3246</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3247</v>
+        <v>3250</v>
       </c>
       <c r="B39" t="s">
-        <v>3248</v>
+        <v>3251</v>
       </c>
       <c r="C39" t="s">
-        <v>3249</v>
+        <v>3252</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -67720,21 +69710,21 @@
         <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="G39" t="s">
-        <v>3246</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3250</v>
+        <v>3253</v>
       </c>
       <c r="B40" t="s">
-        <v>3251</v>
+        <v>3254</v>
       </c>
       <c r="C40" t="s">
-        <v>3249</v>
+        <v>3252</v>
       </c>
       <c r="D40">
         <v>100</v>
@@ -67743,21 +69733,21 @@
         <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>3233</v>
+        <v>3236</v>
       </c>
       <c r="G40" t="s">
-        <v>3246</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3256</v>
+      </c>
+      <c r="C41" t="s">
         <v>3252</v>
-      </c>
-      <c r="B41" t="s">
-        <v>3253</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3249</v>
       </c>
       <c r="D41">
         <v>120</v>
@@ -67766,36 +69756,36 @@
         <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>3165</v>
+        <v>3168</v>
       </c>
       <c r="G41" t="s">
-        <v>3246</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3254</v>
+        <v>3257</v>
       </c>
       <c r="B42" t="s">
-        <v>3255</v>
+        <v>3258</v>
       </c>
       <c r="C42" t="s">
         <v>627</v>
       </c>
       <c r="D42" t="s">
-        <v>3256</v>
+        <v>3259</v>
       </c>
       <c r="E42" t="s">
-        <v>3257</v>
+        <v>3260</v>
       </c>
       <c r="F42" t="s">
-        <v>3156</v>
+        <v>3159</v>
       </c>
       <c r="G42" t="s">
-        <v>3183</v>
+        <v>3186</v>
       </c>
       <c r="H42" t="s">
-        <v>3258</v>
+        <v>3261</v>
       </c>
     </row>
   </sheetData>
@@ -67806,7 +69796,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
@@ -67819,7 +69809,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3259</v>
+        <v>3262</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -67828,22 +69818,22 @@
         <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>3260</v>
+        <v>3263</v>
       </c>
       <c r="E1" t="s">
-        <v>3140</v>
+        <v>3143</v>
       </c>
       <c r="F1" t="s">
-        <v>3141</v>
+        <v>3144</v>
       </c>
       <c r="G1" t="s">
         <v>731</v>
       </c>
       <c r="H1" t="s">
-        <v>3261</v>
+        <v>3264</v>
       </c>
       <c r="I1" t="s">
-        <v>3262</v>
+        <v>3265</v>
       </c>
       <c r="J1" t="s">
         <v>3134</v>
@@ -67854,13 +69844,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3263</v>
+        <v>3266</v>
       </c>
       <c r="B2" t="s">
-        <v>3264</v>
+        <v>3267</v>
       </c>
       <c r="C2" t="s">
-        <v>3265</v>
+        <v>3268</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -67869,15 +69859,15 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>3266</v>
+        <v>3269</v>
       </c>
       <c r="G2" t="s">
-        <v>3267</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3268</v>
+        <v>3271</v>
       </c>
       <c r="B3" t="s">
         <v>572</v>
@@ -67889,7 +69879,7 @@
         <v>627</v>
       </c>
       <c r="E3" t="s">
-        <v>3144</v>
+        <v>3147</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -67901,15 +69891,15 @@
         <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="J3" t="s">
-        <v>3270</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3271</v>
+        <v>3274</v>
       </c>
       <c r="B4" t="s">
         <v>572</v>
@@ -67921,7 +69911,7 @@
         <v>627</v>
       </c>
       <c r="E4" t="s">
-        <v>3144</v>
+        <v>3147</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -67933,10 +69923,42 @@
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="J4" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C5" t="s">
+        <v>573</v>
+      </c>
+      <c r="D5" t="s">
+        <v>627</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3161</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>85</v>
+      </c>
+      <c r="H5">
+        <v>85</v>
+      </c>
+      <c r="I5" t="s">
         <v>3272</v>
+      </c>
+      <c r="J5" t="s">
+        <v>3277</v>
       </c>
     </row>
   </sheetData>
@@ -67947,7 +69969,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -67959,7 +69981,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3260</v>
+        <v>3263</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -67968,37 +69990,37 @@
         <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>3273</v>
+        <v>3278</v>
       </c>
       <c r="E1" t="s">
-        <v>3274</v>
+        <v>3279</v>
       </c>
       <c r="F1" t="s">
-        <v>3275</v>
+        <v>3280</v>
       </c>
       <c r="G1" t="s">
-        <v>3276</v>
+        <v>3281</v>
       </c>
       <c r="H1" t="s">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="I1" t="s">
-        <v>3261</v>
+        <v>3264</v>
       </c>
       <c r="J1" t="s">
-        <v>3278</v>
+        <v>3283</v>
       </c>
       <c r="K1" t="s">
-        <v>3279</v>
+        <v>3284</v>
       </c>
       <c r="L1" t="s">
-        <v>3280</v>
+        <v>3285</v>
       </c>
       <c r="M1" t="s">
         <v>33</v>
       </c>
       <c r="N1" t="s">
-        <v>3281</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
@@ -68006,10 +70028,10 @@
         <v>627</v>
       </c>
       <c r="C2" t="s">
-        <v>3282</v>
+        <v>3287</v>
       </c>
       <c r="D2" t="s">
-        <v>3283</v>
+        <v>3288</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -68021,13 +70043,167 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>3284</v>
+        <v>3289</v>
       </c>
       <c r="M2" t="s">
-        <v>3285</v>
+        <v>3290</v>
       </c>
       <c r="N2" t="s">
-        <v>3286</v>
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3292</v>
+      </c>
+      <c r="I3">
+        <v>200</v>
+      </c>
+      <c r="J3">
+        <v>200</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3289</v>
+      </c>
+      <c r="M3" t="s">
+        <v>3290</v>
+      </c>
+      <c r="N3" t="s">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>627</v>
+      </c>
+      <c r="C4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3292</v>
+      </c>
+      <c r="I4">
+        <v>200</v>
+      </c>
+      <c r="J4">
+        <v>200</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>3289</v>
+      </c>
+      <c r="M4" t="s">
+        <v>3290</v>
+      </c>
+      <c r="N4" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B5" t="s">
+        <v>627</v>
+      </c>
+      <c r="C5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3292</v>
+      </c>
+      <c r="I5">
+        <v>200</v>
+      </c>
+      <c r="J5">
+        <v>200</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>3296</v>
+      </c>
+      <c r="M5" t="s">
+        <v>3290</v>
+      </c>
+      <c r="N5" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B6" t="s">
+        <v>627</v>
+      </c>
+      <c r="C6" t="s">
+        <v>510</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3292</v>
+      </c>
+      <c r="I6">
+        <v>200</v>
+      </c>
+      <c r="J6">
+        <v>200</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>3299</v>
+      </c>
+      <c r="M6" t="s">
+        <v>3290</v>
+      </c>
+      <c r="N6" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C7" t="s">
+        <v>541</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3292</v>
+      </c>
+      <c r="I7">
+        <v>200</v>
+      </c>
+      <c r="J7">
+        <v>200</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>3302</v>
+      </c>
+      <c r="M7" t="s">
+        <v>3290</v>
+      </c>
+      <c r="N7" t="s">
+        <v>3303</v>
       </c>
     </row>
   </sheetData>
@@ -68051,7 +70227,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3287</v>
+        <v>3304</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -68063,82 +70239,82 @@
         <v>617</v>
       </c>
       <c r="E1" t="s">
-        <v>3288</v>
+        <v>3305</v>
       </c>
       <c r="F1" t="s">
-        <v>3289</v>
+        <v>3306</v>
       </c>
       <c r="G1" t="s">
         <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>3290</v>
+        <v>3307</v>
       </c>
       <c r="I1" t="s">
-        <v>3291</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3292</v>
+        <v>3309</v>
       </c>
       <c r="B2" t="s">
-        <v>3293</v>
+        <v>3310</v>
       </c>
       <c r="C2" t="s">
-        <v>3294</v>
+        <v>3311</v>
       </c>
       <c r="D2" t="s">
-        <v>3295</v>
+        <v>3312</v>
       </c>
       <c r="E2" t="s">
-        <v>3296</v>
+        <v>3313</v>
       </c>
       <c r="F2" t="s">
         <v>612</v>
       </c>
       <c r="G2" t="s">
-        <v>3297</v>
+        <v>3136</v>
       </c>
       <c r="H2" t="s">
-        <v>3298</v>
+        <v>3314</v>
       </c>
       <c r="I2" t="s">
-        <v>3299</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3300</v>
+        <v>3316</v>
       </c>
       <c r="B3" t="s">
-        <v>3301</v>
+        <v>3317</v>
       </c>
       <c r="C3" t="s">
-        <v>3302</v>
+        <v>3318</v>
       </c>
       <c r="D3" t="s">
-        <v>3303</v>
+        <v>3319</v>
       </c>
       <c r="E3" t="s">
-        <v>3304</v>
+        <v>3320</v>
       </c>
       <c r="F3" t="s">
-        <v>3305</v>
+        <v>3321</v>
       </c>
       <c r="G3" t="s">
-        <v>3297</v>
+        <v>3136</v>
       </c>
       <c r="H3" t="s">
-        <v>3306</v>
+        <v>3322</v>
       </c>
       <c r="I3" t="s">
-        <v>3307</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3308</v>
+        <v>3324</v>
       </c>
       <c r="B4" t="s">
         <v>627</v>
@@ -68150,10 +70326,10 @@
         <v>612</v>
       </c>
       <c r="G4" t="s">
-        <v>3309</v>
+        <v>3136</v>
       </c>
       <c r="H4" t="s">
-        <v>3310</v>
+        <v>3325</v>
       </c>
       <c r="I4" t="s">
         <v>627</v>

--- a/backend/src/data/hospital-data.xlsx
+++ b/backend/src/data/hospital-data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15125" uniqueCount="3570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15159" uniqueCount="3581">
   <si>
     <t>User ID</t>
   </si>
@@ -9934,6 +9934,12 @@
     <t>2026-06-08T09:19:50.766Z</t>
   </si>
   <si>
+    <t>BILL-D4AC91</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:12:56.326Z</t>
+  </si>
+  <si>
     <t>Procedure ID</t>
   </si>
   <si>
@@ -10730,6 +10736,33 @@
   </si>
   <si>
     <t>2026-06-08T10:46:12.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:12:56.659Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:12:56.956Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:02.749Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:11.777Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:12.972Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:35.442Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:37.642Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:40.640Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T12:13:42.665Z</t>
   </si>
 </sst>
 </file>
@@ -11209,7 +11242,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -11222,2409 +11255,2508 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3326</v>
+        <v>3328</v>
       </c>
       <c r="B1" t="s">
-        <v>3327</v>
+        <v>3329</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3328</v>
+        <v>3330</v>
       </c>
       <c r="E1" t="s">
-        <v>3329</v>
+        <v>3331</v>
       </c>
       <c r="F1" t="s">
-        <v>3330</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3331</v>
+        <v>3333</v>
       </c>
       <c r="C2" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E2" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>3336</v>
+      </c>
+      <c r="C3" t="s">
         <v>3334</v>
       </c>
-      <c r="C3" t="s">
-        <v>3332</v>
-      </c>
       <c r="E3" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>3337</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E4" t="s">
         <v>3335</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3332</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3333</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3336</v>
+        <v>3338</v>
       </c>
       <c r="C5" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E5" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3337</v>
+        <v>3339</v>
       </c>
       <c r="C6" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E6" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3339</v>
+        <v>3341</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>3340</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3341</v>
+        <v>3343</v>
       </c>
       <c r="C8" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E8" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3342</v>
+        <v>3344</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>3340</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3343</v>
+        <v>3345</v>
       </c>
       <c r="C10" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E10" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3344</v>
+        <v>3346</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>3340</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3345</v>
+        <v>3347</v>
       </c>
       <c r="C12" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E12" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3346</v>
+        <v>3348</v>
       </c>
       <c r="C13" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E13" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3347</v>
+        <v>3349</v>
       </c>
       <c r="C14" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E14" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3348</v>
+        <v>3350</v>
       </c>
       <c r="C15" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E15" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3349</v>
+        <v>3351</v>
       </c>
       <c r="C16" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E16" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3350</v>
+        <v>3352</v>
       </c>
       <c r="C17" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E17" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3351</v>
+        <v>3353</v>
       </c>
       <c r="C18" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E18" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3352</v>
+        <v>3354</v>
       </c>
       <c r="C19" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E19" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3353</v>
+        <v>3355</v>
       </c>
       <c r="C20" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E20" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3354</v>
+        <v>3356</v>
       </c>
       <c r="C21" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E21" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3355</v>
+        <v>3357</v>
       </c>
       <c r="C22" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E22" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3356</v>
+        <v>3358</v>
       </c>
       <c r="C23" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E23" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3357</v>
+        <v>3359</v>
       </c>
       <c r="C24" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E24" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3358</v>
+        <v>3360</v>
       </c>
       <c r="C25" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E25" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3359</v>
+        <v>3361</v>
       </c>
       <c r="C26" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E26" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3360</v>
+        <v>3362</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>3340</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3361</v>
+        <v>3363</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>3362</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3363</v>
+        <v>3365</v>
       </c>
       <c r="C29" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E29" t="s">
-        <v>3364</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3365</v>
+        <v>3367</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3367</v>
+        <v>3369</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>3368</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3369</v>
+        <v>3371</v>
       </c>
       <c r="C32" t="s">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>3368</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3370</v>
+        <v>3372</v>
       </c>
       <c r="C33" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E33" t="s">
-        <v>3371</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3372</v>
+        <v>3374</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>3373</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3374</v>
+        <v>3376</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3377</v>
+        <v>3379</v>
       </c>
       <c r="C37" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E37" t="s">
-        <v>3378</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>3380</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3381</v>
+        <v>3383</v>
       </c>
       <c r="C39" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E39" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="C40" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E40" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3383</v>
+        <v>3385</v>
       </c>
       <c r="C41" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E41" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3384</v>
+        <v>3386</v>
       </c>
       <c r="C42" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E42" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3385</v>
+        <v>3387</v>
       </c>
       <c r="C43" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E43" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3386</v>
+        <v>3388</v>
       </c>
       <c r="C44" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E44" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3387</v>
+        <v>3389</v>
       </c>
       <c r="C45" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E45" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3388</v>
+        <v>3390</v>
       </c>
       <c r="C46" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E46" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3389</v>
+        <v>3391</v>
       </c>
       <c r="C47" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E47" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3390</v>
+        <v>3392</v>
       </c>
       <c r="C48" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E48" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3391</v>
+        <v>3393</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>3340</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3392</v>
+        <v>3394</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>3362</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3393</v>
+        <v>3395</v>
       </c>
       <c r="C51" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E51" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3394</v>
+        <v>3396</v>
       </c>
       <c r="C52" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E52" t="s">
-        <v>3395</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3396</v>
+        <v>3398</v>
       </c>
       <c r="C53" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E53" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3397</v>
+        <v>3399</v>
       </c>
       <c r="C54" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E54" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3398</v>
+        <v>3400</v>
       </c>
       <c r="C55" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E55" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3399</v>
+        <v>3401</v>
       </c>
       <c r="C56" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E56" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3400</v>
+        <v>3402</v>
       </c>
       <c r="C57" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E57" t="s">
-        <v>3338</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3401</v>
+        <v>3403</v>
       </c>
       <c r="C58" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E58" t="s">
-        <v>3395</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3402</v>
+        <v>3404</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>3340</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3403</v>
+        <v>3405</v>
       </c>
       <c r="C60" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E60" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3404</v>
+        <v>3406</v>
       </c>
       <c r="C61" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E61" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3405</v>
+        <v>3407</v>
       </c>
       <c r="C62" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E62" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3406</v>
+        <v>3408</v>
       </c>
       <c r="C63" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E63" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3407</v>
+        <v>3409</v>
       </c>
       <c r="C64" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E64" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3408</v>
+        <v>3410</v>
       </c>
       <c r="C65" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E65" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3409</v>
+        <v>3411</v>
       </c>
       <c r="C66" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E66" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3410</v>
+        <v>3412</v>
       </c>
       <c r="C67" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E67" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3411</v>
+        <v>3413</v>
       </c>
       <c r="C68" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E68" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3413</v>
+        <v>3415</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3415</v>
+        <v>3417</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3416</v>
+        <v>3418</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3417</v>
+        <v>3419</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3418</v>
+        <v>3420</v>
       </c>
       <c r="C73" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E73" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3419</v>
+        <v>3421</v>
       </c>
       <c r="C74" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E74" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3420</v>
+        <v>3422</v>
       </c>
       <c r="C75" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E75" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3421</v>
+        <v>3423</v>
       </c>
       <c r="C76" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E76" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3422</v>
+        <v>3424</v>
       </c>
       <c r="C77" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E77" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>3423</v>
+        <v>3425</v>
       </c>
       <c r="C78" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E78" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>3424</v>
+        <v>3426</v>
       </c>
       <c r="C79" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E79" t="s">
-        <v>3425</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3426</v>
+        <v>3428</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
       </c>
       <c r="E80" t="s">
-        <v>3427</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3428</v>
+        <v>3430</v>
       </c>
       <c r="C81" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E81" t="s">
-        <v>3425</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>3429</v>
+        <v>3431</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
       </c>
       <c r="E82" t="s">
-        <v>3427</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>3430</v>
+        <v>3432</v>
       </c>
       <c r="C83" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E83" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>3431</v>
+        <v>3433</v>
       </c>
       <c r="C84" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E84" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>3432</v>
+        <v>3434</v>
       </c>
       <c r="C85" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E85" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3433</v>
+        <v>3435</v>
       </c>
       <c r="C86" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E86" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>3434</v>
+        <v>3436</v>
       </c>
       <c r="C87" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E87" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>3435</v>
+        <v>3437</v>
       </c>
       <c r="C88" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E88" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3436</v>
+        <v>3438</v>
       </c>
       <c r="C89" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E89" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="C90" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E90" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>3438</v>
+        <v>3440</v>
       </c>
       <c r="C91" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E91" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>3439</v>
+        <v>3441</v>
       </c>
       <c r="C92" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E92" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>3440</v>
+        <v>3442</v>
       </c>
       <c r="C93" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E93" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>3441</v>
+        <v>3443</v>
       </c>
       <c r="C94" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E94" t="s">
-        <v>3364</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>3442</v>
+        <v>3444</v>
       </c>
       <c r="C95" t="s">
         <v>8</v>
       </c>
       <c r="E95" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>3443</v>
+        <v>3445</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>3444</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>3445</v>
+        <v>3447</v>
       </c>
       <c r="C97" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E97" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>3446</v>
+        <v>3448</v>
       </c>
       <c r="C98" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E98" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="C99" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E99" t="s">
-        <v>3425</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>3448</v>
+        <v>3450</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>3427</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>3449</v>
+        <v>3451</v>
       </c>
       <c r="C101" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E101" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>3450</v>
+        <v>3452</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
       </c>
       <c r="E102" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>3451</v>
+        <v>3453</v>
       </c>
       <c r="C103" t="s">
         <v>8</v>
       </c>
       <c r="E103" t="s">
-        <v>3452</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>3453</v>
+        <v>3455</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
       </c>
       <c r="E104" t="s">
-        <v>3452</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>3454</v>
+        <v>3456</v>
       </c>
       <c r="C105" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E105" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>3455</v>
+        <v>3457</v>
       </c>
       <c r="C106" t="s">
         <v>8</v>
       </c>
       <c r="E106" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>3456</v>
+        <v>3458</v>
       </c>
       <c r="C107" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E107" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>3457</v>
+        <v>3459</v>
       </c>
       <c r="C108" t="s">
         <v>8</v>
       </c>
       <c r="E108" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>3458</v>
+        <v>3460</v>
       </c>
       <c r="C109" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E109" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>3459</v>
+        <v>3461</v>
       </c>
       <c r="C110" t="s">
         <v>8</v>
       </c>
       <c r="E110" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3460</v>
+        <v>3462</v>
       </c>
       <c r="C111" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E111" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>3461</v>
+        <v>3463</v>
       </c>
       <c r="C112" t="s">
         <v>8</v>
       </c>
       <c r="E112" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>3462</v>
+        <v>3464</v>
       </c>
       <c r="C113" t="s">
         <v>8</v>
       </c>
       <c r="E113" t="s">
-        <v>3452</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>3463</v>
+        <v>3465</v>
       </c>
       <c r="C114" t="s">
         <v>8</v>
       </c>
       <c r="E114" t="s">
-        <v>3464</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>3465</v>
+        <v>3467</v>
       </c>
       <c r="C115" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E115" t="s">
-        <v>3412</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>3466</v>
+        <v>3468</v>
       </c>
       <c r="C116" t="s">
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>3414</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>3467</v>
+        <v>3469</v>
       </c>
       <c r="C117" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E117" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>3468</v>
+        <v>3470</v>
       </c>
       <c r="C118" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E118" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3469</v>
+        <v>3471</v>
       </c>
       <c r="C119" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E119" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>3470</v>
+        <v>3472</v>
       </c>
       <c r="C120" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E120" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>3471</v>
+        <v>3473</v>
       </c>
       <c r="C121" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E121" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>3472</v>
+        <v>3474</v>
       </c>
       <c r="C122" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E122" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>3473</v>
+        <v>3475</v>
       </c>
       <c r="C123" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E123" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>3474</v>
+        <v>3476</v>
       </c>
       <c r="C124" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E124" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="C125" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E125" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>3476</v>
+        <v>3478</v>
       </c>
       <c r="C126" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E126" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>3477</v>
+        <v>3479</v>
       </c>
       <c r="C127" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E127" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>3478</v>
+        <v>3480</v>
       </c>
       <c r="C128" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E128" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>3479</v>
+        <v>3481</v>
       </c>
       <c r="C129" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E129" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>3480</v>
+        <v>3482</v>
       </c>
       <c r="C130" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E130" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>3481</v>
+        <v>3483</v>
       </c>
       <c r="C131" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E131" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>3482</v>
+        <v>3484</v>
       </c>
       <c r="C132" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E132" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>3483</v>
+        <v>3485</v>
       </c>
       <c r="C133" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E133" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>3484</v>
+        <v>3486</v>
       </c>
       <c r="C134" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E134" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3485</v>
+        <v>3487</v>
       </c>
       <c r="C135" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E135" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>3486</v>
+        <v>3488</v>
       </c>
       <c r="C136" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E136" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>3487</v>
+        <v>3489</v>
       </c>
       <c r="C137" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E137" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>3488</v>
+        <v>3490</v>
       </c>
       <c r="C138" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E138" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>3489</v>
+        <v>3491</v>
       </c>
       <c r="C139" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E139" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>3490</v>
+        <v>3492</v>
       </c>
       <c r="C140" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E140" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>3491</v>
+        <v>3493</v>
       </c>
       <c r="C141" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E141" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>3492</v>
+        <v>3494</v>
       </c>
       <c r="C142" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E142" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>3493</v>
+        <v>3495</v>
       </c>
       <c r="C143" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E143" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>3494</v>
+        <v>3496</v>
       </c>
       <c r="C144" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E144" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>3495</v>
+        <v>3497</v>
       </c>
       <c r="C145" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E145" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>3496</v>
+        <v>3498</v>
       </c>
       <c r="C146" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E146" t="s">
-        <v>3364</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>3497</v>
+        <v>3499</v>
       </c>
       <c r="C147" t="s">
         <v>8</v>
       </c>
       <c r="E147" t="s">
-        <v>3366</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>3498</v>
+        <v>3500</v>
       </c>
       <c r="C148" t="s">
         <v>8</v>
       </c>
       <c r="E148" t="s">
-        <v>3368</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>3499</v>
+        <v>3501</v>
       </c>
       <c r="C149" t="s">
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>3368</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>3500</v>
+        <v>3502</v>
       </c>
       <c r="C150" t="s">
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>3501</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>3502</v>
+        <v>3504</v>
       </c>
       <c r="C151" t="s">
         <v>8</v>
       </c>
       <c r="E151" t="s">
-        <v>3501</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>3503</v>
+        <v>3505</v>
       </c>
       <c r="C152" t="s">
         <v>8</v>
       </c>
       <c r="E152" t="s">
-        <v>3501</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>3504</v>
+        <v>3506</v>
       </c>
       <c r="C153" t="s">
         <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>3452</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>3505</v>
+        <v>3507</v>
       </c>
       <c r="C154" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E154" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>3506</v>
+        <v>3508</v>
       </c>
       <c r="C155" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E155" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>3507</v>
+        <v>3509</v>
       </c>
       <c r="C156" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E156" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>3508</v>
+        <v>3510</v>
       </c>
       <c r="C157" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E157" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>3509</v>
+        <v>3511</v>
       </c>
       <c r="C158" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E158" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>3510</v>
+        <v>3512</v>
       </c>
       <c r="C159" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E159" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>3511</v>
+        <v>3513</v>
       </c>
       <c r="C160" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E160" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>3512</v>
+        <v>3514</v>
       </c>
       <c r="C161" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E161" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>3513</v>
+        <v>3515</v>
       </c>
       <c r="C162" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E162" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>3514</v>
+        <v>3516</v>
       </c>
       <c r="C163" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E163" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>3515</v>
+        <v>3517</v>
       </c>
       <c r="C164" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E164" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>3516</v>
+        <v>3518</v>
       </c>
       <c r="C165" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E165" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>3517</v>
+        <v>3519</v>
       </c>
       <c r="C166" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E166" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>3518</v>
+        <v>3520</v>
       </c>
       <c r="C167" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E167" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>3519</v>
+        <v>3521</v>
       </c>
       <c r="C168" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E168" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>3520</v>
+        <v>3522</v>
       </c>
       <c r="C169" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E169" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>3521</v>
+        <v>3523</v>
       </c>
       <c r="C170" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E170" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>3522</v>
+        <v>3524</v>
       </c>
       <c r="C171" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E171" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>3523</v>
+        <v>3525</v>
       </c>
       <c r="C172" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E172" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>3524</v>
+        <v>3526</v>
       </c>
       <c r="C173" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E173" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>3525</v>
+        <v>3527</v>
       </c>
       <c r="C174" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E174" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>3526</v>
+        <v>3528</v>
       </c>
       <c r="C175" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E175" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>3527</v>
+        <v>3529</v>
       </c>
       <c r="C176" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E176" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>3528</v>
+        <v>3530</v>
       </c>
       <c r="C177" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E177" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>3529</v>
+        <v>3531</v>
       </c>
       <c r="C178" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E178" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>3530</v>
+        <v>3532</v>
       </c>
       <c r="C179" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E179" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>3531</v>
+        <v>3533</v>
       </c>
       <c r="C180" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E180" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="C181" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E181" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>3533</v>
+        <v>3535</v>
       </c>
       <c r="C182" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E182" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>3534</v>
+        <v>3536</v>
       </c>
       <c r="C183" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E183" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="C184" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E184" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="C185" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E185" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="C186" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E186" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>3538</v>
+        <v>3540</v>
       </c>
       <c r="C187" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E187" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="C188" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E188" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="C189" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E189" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="C190" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E190" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>3542</v>
+        <v>3544</v>
       </c>
       <c r="C191" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E191" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>3543</v>
+        <v>3545</v>
       </c>
       <c r="C192" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E192" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>3544</v>
+        <v>3546</v>
       </c>
       <c r="C193" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E193" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>3545</v>
+        <v>3547</v>
       </c>
       <c r="C194" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E194" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>3546</v>
+        <v>3548</v>
       </c>
       <c r="C195" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E195" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>3547</v>
+        <v>3549</v>
       </c>
       <c r="C196" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E196" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>3548</v>
+        <v>3550</v>
       </c>
       <c r="C197" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E197" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="C198" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E198" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3550</v>
+        <v>3552</v>
       </c>
       <c r="C199" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E199" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>3551</v>
+        <v>3553</v>
       </c>
       <c r="C200" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E200" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>3552</v>
+        <v>3554</v>
       </c>
       <c r="C201" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E201" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>3553</v>
+        <v>3555</v>
       </c>
       <c r="C202" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E202" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>3554</v>
+        <v>3556</v>
       </c>
       <c r="C203" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E203" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>3555</v>
+        <v>3557</v>
       </c>
       <c r="C204" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E204" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>3556</v>
+        <v>3558</v>
       </c>
       <c r="C205" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E205" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>3557</v>
+        <v>3559</v>
       </c>
       <c r="C206" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E206" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>3558</v>
+        <v>3560</v>
       </c>
       <c r="C207" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E207" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>3559</v>
+        <v>3561</v>
       </c>
       <c r="C208" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E208" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>3560</v>
+        <v>3562</v>
       </c>
       <c r="C209" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E209" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>3561</v>
+        <v>3563</v>
       </c>
       <c r="C210" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E210" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>3562</v>
+        <v>3564</v>
       </c>
       <c r="C211" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E211" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>3563</v>
+        <v>3565</v>
       </c>
       <c r="C212" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E212" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>3564</v>
+        <v>3566</v>
       </c>
       <c r="C213" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E213" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>3565</v>
+        <v>3567</v>
       </c>
       <c r="C214" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E214" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>3566</v>
+        <v>3568</v>
       </c>
       <c r="C215" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E215" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>3567</v>
+        <v>3569</v>
       </c>
       <c r="C216" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E216" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>3568</v>
+        <v>3570</v>
       </c>
       <c r="C217" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E217" t="s">
-        <v>3333</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>3569</v>
+        <v>3571</v>
       </c>
       <c r="C218" t="s">
-        <v>3332</v>
+        <v>3334</v>
       </c>
       <c r="E218" t="s">
-        <v>3333</v>
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>3572</v>
+      </c>
+      <c r="C219" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E219" t="s">
+        <v>3414</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>3573</v>
+      </c>
+      <c r="C220" t="s">
+        <v>8</v>
+      </c>
+      <c r="E220" t="s">
+        <v>3416</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>3574</v>
+      </c>
+      <c r="C221" t="s">
+        <v>8</v>
+      </c>
+      <c r="E221" t="s">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>3575</v>
+      </c>
+      <c r="C222" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E222" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>3576</v>
+      </c>
+      <c r="C223" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E223" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>3577</v>
+      </c>
+      <c r="C224" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E224" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>3578</v>
+      </c>
+      <c r="C225" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E225" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>3579</v>
+      </c>
+      <c r="C226" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E226" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>3580</v>
+      </c>
+      <c r="C227" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E227" t="s">
+        <v>3335</v>
       </c>
     </row>
   </sheetData>
@@ -69969,7 +70101,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -70204,6 +70336,38 @@
       </c>
       <c r="N7" t="s">
         <v>3303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B8" t="s">
+        <v>627</v>
+      </c>
+      <c r="C8" t="s">
+        <v>488</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3292</v>
+      </c>
+      <c r="I8">
+        <v>200</v>
+      </c>
+      <c r="J8">
+        <v>200</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>3302</v>
+      </c>
+      <c r="M8" t="s">
+        <v>3290</v>
+      </c>
+      <c r="N8" t="s">
+        <v>3305</v>
       </c>
     </row>
   </sheetData>
@@ -70227,7 +70391,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3304</v>
+        <v>3306</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -70239,36 +70403,36 @@
         <v>617</v>
       </c>
       <c r="E1" t="s">
-        <v>3305</v>
+        <v>3307</v>
       </c>
       <c r="F1" t="s">
-        <v>3306</v>
+        <v>3308</v>
       </c>
       <c r="G1" t="s">
         <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>3307</v>
+        <v>3309</v>
       </c>
       <c r="I1" t="s">
-        <v>3308</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3309</v>
+        <v>3311</v>
       </c>
       <c r="B2" t="s">
-        <v>3310</v>
+        <v>3312</v>
       </c>
       <c r="C2" t="s">
-        <v>3311</v>
+        <v>3313</v>
       </c>
       <c r="D2" t="s">
-        <v>3312</v>
+        <v>3314</v>
       </c>
       <c r="E2" t="s">
-        <v>3313</v>
+        <v>3315</v>
       </c>
       <c r="F2" t="s">
         <v>612</v>
@@ -70277,44 +70441,44 @@
         <v>3136</v>
       </c>
       <c r="H2" t="s">
-        <v>3314</v>
+        <v>3316</v>
       </c>
       <c r="I2" t="s">
-        <v>3315</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3316</v>
+        <v>3318</v>
       </c>
       <c r="B3" t="s">
-        <v>3317</v>
+        <v>3319</v>
       </c>
       <c r="C3" t="s">
-        <v>3318</v>
+        <v>3320</v>
       </c>
       <c r="D3" t="s">
-        <v>3319</v>
+        <v>3321</v>
       </c>
       <c r="E3" t="s">
-        <v>3320</v>
+        <v>3322</v>
       </c>
       <c r="F3" t="s">
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="G3" t="s">
         <v>3136</v>
       </c>
       <c r="H3" t="s">
-        <v>3322</v>
+        <v>3324</v>
       </c>
       <c r="I3" t="s">
-        <v>3323</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3324</v>
+        <v>3326</v>
       </c>
       <c r="B4" t="s">
         <v>627</v>
@@ -70329,7 +70493,7 @@
         <v>3136</v>
       </c>
       <c r="H4" t="s">
-        <v>3325</v>
+        <v>3327</v>
       </c>
       <c r="I4" t="s">
         <v>627</v>
